--- a/docs/FCC-core-55-70/build-analysis-july24.xlsx
+++ b/docs/FCC-core-55-70/build-analysis-july24.xlsx
@@ -7,18 +7,19 @@
   </bookViews>
   <sheets>
     <sheet name="How to read" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SUMMARY — read me first" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Build 46 — findings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Build 47 — findings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Examples &amp; mock map" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="UX design v1.1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Design — Invest·CF·Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Design — Home·Net worth" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Strategy &amp; data lineage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="PRD v1.1" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Build 47 — plan" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Build 48 — payload" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Build 48 — findings" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Built — Aug 11" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SUMMARY — read me first" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Build 46 — findings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Build 47 — findings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Examples &amp; mock map" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="UX design v1.1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Design — Invest·CF·Plan" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Design — Home·Net worth" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Strategy &amp; data lineage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PRD v1.1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Build 47 — plan" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Build 48 — payload" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Build 48 — findings" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +93,11 @@
     <font>
       <sz val="10.5"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +117,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001B2A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00085041"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFF2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAEEDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -195,6 +214,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -652,6 +678,451 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Where (doc tab · row)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>The document says</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>The code actually does (file evidence)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>What it means for you / recommended action</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Build status — proposed vs built (added 2026-07-29; kept current)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Strategy · bank connection</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>The one big new capability v1 depends on.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERED AND LIVE — SnapTrade relay deployed, the relay address ships in the app config, and your own E*TRADE connection proved it end-to-end. (The auditor flagged it inactive; I corrected this — the config wiring commit and your live connection are the evidence.)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERED</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Remaining gated pieces: Fidelity application, plan upgrade before beta, Teller/banks for checking-account coverage.</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>DELIVERED — live and verified; remaining founder-gated: Fidelity application, plan upgrade before beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Strategy · "your data stays yours"</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Privacy positioning.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The consent honestly says data flows through the connection service read-only and is deletable (sync/index.ts:77-85) — a relay, not local-only.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>DELIVERED (nuanced)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The in-app copy is honest. Make sure marketing copy matches the same honest framing, never "we never see your data."</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>DELIVERED — in-app copy is honest; keep marketing copy to the same standard (your side, when written)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Strategy · market-comparison hook</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>"How you're doing against the market" is the weekly habit hook.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Works today on an unofficial free price feed (marketData.ts:25); the keyed-provider seam is ready but the provider decision is open.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FOUNDER-GATED</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The core hook rides an endpoint that can break without notice. The price-provider decision is the highest-leverage open external.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ONE-PAGER DELIVERED — awaiting your pick · docs/FCC-core-55-70/price-provider-onepager-v1-2026-07-29.xlsx (recommend Intrinio, fallback Twelve Data Venture; your 2-minute email inside)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Strategy · out-of-scope surfaces still shipped</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Estate, insurance, deep tax organizer are out of scope for v1.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>The pre-FCC screens still exist and are routed (app/estate.tsx, insurance.tsx, tax-organizer.tsx, itemize.tsx, jobsafety.tsx, credit.tsx).</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>OPEN DECISION</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Keep them (extra value, review burden) or hide them for launch (focus, less to test). 97-row sign-off includes them either way — your call.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-07-28 — keep in v1; the five modules stay in your 97-row sign-off walk (action item 41)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Lineage · market average duplicated</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>The market-comparison number comes from one shared helper.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Identical formula pasted inline in BOTH Home and Invest (HomeScreen.tsx:151-155, PerformanceScreen.tsx:72-74). Two auditors confirmed.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>CODE GAP</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Values agree today because the copies match. One edit to one copy breaks your one-number rule silently. Extract the helper + agreement pin.</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>BUILT — riding Build 46 (v1.1.0 #46, CUT 2026-07-29) · pinned by tests · walk it on TestFlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Lineage · Roth math orphaned</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>The Roth screen computes its tax-now via the shared rothConversion helper.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>The screen does its own inline marginal-tax math; the helper has zero callers (RothScreen.tsx:46).</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>CODE GAP</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Same one-number risk. Either wire the helper or delete it — an orphaned duplicate concept is a trap.</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Lineage · two savings-capacity helpers</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>One capacity concept.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Goals uses one helper, multi-goal/cash-flow another; they coexist (GoalsScreen.tsx:37 vs MultiGoalScreen.tsx:58).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CODE GAP</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Consolidate to one before they drift.</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Lineage · scenario-diff hand-built</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>A shared diff helper feeds the adoption sheet.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Each screen hand-builds its diff rows; adopt/revert/history machinery IS shared (useStore.ts:783-791).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CODE GAP</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation candidate — becomes urgent when the adoption sheet is upgraded (see Plan tab).</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PARKED — rides the adoption-sheet rebuild (action item 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Lineage · source-chip wording ×3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>One shared source-chip component.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Three inline variants with diverging wording (NetWorthScreen.tsx:159-161 vs AccountDetailScreen.tsx:60 vs SettingsScreen.tsx:417).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CODE GAP</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Same fix class as the estimate chip: one component, one wording.</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Lineage · RMD growth math</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Future-year required withdrawals use the shared projection engine.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>The schedule grows balances by its own rule instead (decumulation/index.ts:47-59).</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>CODE GAP</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Minor divergence risk between the RMD table and other projections; align when touched next.</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>(coverage)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Strategy: 15 commitments checked, 11 delivered as promised. Lineage: 98 rows checked, 78 verified — the named helper really feeds the named screen.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Verified delivered: scenarios suite, confidence engine, quantified non-advice nudges, multi-goal in v1, milestones, estimate labeling, zero advice language, no parent-sharing (correctly cut).</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The one-concept-one-helper rule holds on 78 of 98 rows; the exceptions above are the complete list.</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>— context/coverage row · nothing to build</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -1196,7 +1667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1394,7 +1865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1560,7 +2031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1832,7 +2303,623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="94" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>What was asked for / what was wrong</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>What is built</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Where it came from</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>— NET WORTH · the Quiet Instrument rebuild —</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr"/>
+      <c r="C2" s="21" t="inlineStr"/>
+      <c r="D2" s="21" t="inlineStr"/>
+      <c r="E2" s="21" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Net worth · the whole screen</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Claude Design "Quiet Instrument" handoff + the founder's 11 hero corrections</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Flat continuous ledger; one shared right edge for every number; hero title carries only the info dot then the date; the trend line under the hero deleted; change line reads "Change in net worth +$X · Return on cash + investments +Y%", green at zero and up, amber only on a fall; since-line plain weight with the year.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Handoff + NW-screen.docx, 2026-08-10</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — in build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Net worth · the six decisions</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Founder decisions on the audit workbook</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Composition bar replaces the donut; What you owe gains its own bar; the cushion gains a progress bar; categories read biggest-first; the cash-flow row deleted; grouping buttons on day one.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Audit workbook "Round 2", 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — in build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>All screens · section banners</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Square corners, applied everywhere</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SectionBand corners squared — one component, so every banded screen changed at once. Hero and retirement plan wear the same full-width banner as WHAT YOU OWN.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — in build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>All screens · the money column</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>One size, totals bold, genuinely right-aligned</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Every money figure 15pt, totals bold. AND the column was really bent: band totals sat 8 points right of row values because a row puts a gap before its arrow and a band did not. One constant now; the test MEASURES both edges instead of asserting a margin.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Founder, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — in build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>All screens · account naming</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>THE naming rule</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Taxable = institution + last four ("Vanguard -5738"); no digits = institution + account word; tax-advantaged = institution + wrapper + last four; duplicates get · 1 / · 2. Only real digits qualify. Recorded in the PRD (Amendments + Sameness contract).</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Founder rule, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>— CONNECTIONS · honesty —</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Net worth · "Sync now"</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>The button did not sync — it opened a page that cannot sync</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>It runs the sync in place, shows "Syncing…", and reports the real count. Saying "Updated" when nothing refreshed is gone.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Founder device finding, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Net worth · dead connections</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>No way to re-log-in, and a dead link looked identical to a healthy one</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Per-account sync failures are recorded; the row reads "We couldn't reach Vanguard -5738" with a RECONNECT button. An account marked connected with NO connection at the provider is recorded too, instead of ageing silently.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Founder device finding, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Everywhere · two dead routes</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Buttons that led to screens which do not exist</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>First-day "Connect a brokerage" and the fix-it sheet's "Update the value" both fixed; a new guard walks every pushed route and fails on any that names no screen.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Found during the rebuild audit</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — in build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>— CLASSIFICATION · cash means cash —</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="21" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Assets · the cash-only rule</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Applied in the migration but NOT where data arrives</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>The name/ticker rule is applied at classification, so a holding synced after the migration cannot land back in Cash. Known money-market tickers (VMFXX, SPAXX, SWVXX…) are recognised when a broker sends only a symbol.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Founder correction, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Assets · the unexplained leftover</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Counted as MORE of the biggest holding</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>A positive leftover is CASH — it is money the broker's total includes but its holdings do not itemise. A negative leftover stays a pricing artifact. This was the chain that turned a $500 deposit into "more CDs".</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Founder question, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Transactions · a deposit</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Had nowhere to land, so it only inflated the total</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>A deposit into an account that itemises holdings opens the cash sleeve and lands there; the total rises by the same amount. The sheet says so: "Lands as cash in this account."</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Founder finding, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>— THE RETIREMENT PLAN —</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="21" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Net worth + Plan · the verdict</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Went silent below 80% odds — a bare "See your plan"</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>It speaks for every computable plan and tells the truth about the ending: "to spare" only when there is something spare, otherwise "running short around age 84". The word now carries its number, in ONE wording used on Home, Net worth and Plan: "&lt;word&gt; — xx% odds of lasting to age abc".</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Founder finding + rule, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Plan · the three questions</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>A line naming one missing answer landed on a hub, then on a 7-item checklist</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>NEW /plan-answers: asks what the odds are missing, prefilled with what we hold, ?focus= opens at one, shows the odds on the same screen, returns you where you came from. Home, Net worth and Plan all open it. The app had NO screen capturing age at all before this.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Founder finding, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Plan · what counts toward retirement</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Cash and all property were excluded by default</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Everything counts except the home you live in and the car you drive; a rental and a second car count. Changeable per account on the answers screen, and the person's choice always beats the default.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Founder rule, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Plan · the odds model</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>"Where do the assumptions come from?"</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Volatility is MEASURED per asset class from the same long-run series as the returns (was return × 1.7). The info dot explains the whole method in plain English with every number and where to change it, and it SCROLLS — the text was previously unreadable past the fold. The full model is recorded in the PRD ("Retirement odds — assumptions", 45 rows).</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Founder questions, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>— ACCOUNT DETAIL + PERFORMANCE —</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr"/>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Account detail · income</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Untickered income was pinned onto every holding</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>A holding claims income only when the source names it — no CD shows "dividends" any more. Untickered income is still counted at the account level. The activity list is newest-first, so income is no longer hidden past the cut.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Founder finding, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Account detail · whose fact is a row</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Broker records and your own looked identical</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Your rows wear "you entered this" and a pencil; broker rows read "from Vanguard" and are read-only. A correction reverses the old amount and records the new one through the one engine. The door names the date the list stops at.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Performance handoff, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Performance · the walks</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Per-account walks skipped accounts with no itemised holdings</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Every account with value gets its walk, so the parts sum to the all-accounts walk — which is titled "· ALL ACCOUNTS" as the handoff names it.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Performance handoff, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>BUILT — after build 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Performance · still open</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Two items deliberately not built</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Category rows tapping through to a category-detail screen (a new screen). The handoff's "/yr" stated-yield treatment for bonds and cash (a CALCULATION change — the founder's instruction was to take the UX, not the calculations).</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Performance handoff, 2026-08-11</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>OPEN — founder's call</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2145,12 +3232,44 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Built — Aug 11 (this file)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>The Net worth Quiet-Instrument rebuild, the founder's device findings from builds 51 and 52, and the Performance/account-detail handoff.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>See the "Built — Aug 11" tab: 18 items with what was wrong, what is built and where it came from.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>BUILT (build 52 + after)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Two Performance items remain open by the founder's own instruction — a category-detail screen, and the "/yr" stated-yield treatment (a calculation change).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2448,7 +3567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2846,7 +3965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4737,7 +5856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5497,7 +6616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6642,7 +7761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7505,449 +8624,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Where (doc tab · row)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>The document says</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>The code actually does (file evidence)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>What it means for you / recommended action</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>Build status — proposed vs built (added 2026-07-29; kept current)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="80" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Strategy · bank connection</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>The one big new capability v1 depends on.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>DELIVERED AND LIVE — SnapTrade relay deployed, the relay address ships in the app config, and your own E*TRADE connection proved it end-to-end. (The auditor flagged it inactive; I corrected this — the config wiring commit and your live connection are the evidence.)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>DELIVERED</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Remaining gated pieces: Fidelity application, plan upgrade before beta, Teller/banks for checking-account coverage.</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>DELIVERED — live and verified; remaining founder-gated: Fidelity application, plan upgrade before beta</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Strategy · "your data stays yours"</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Privacy positioning.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>The consent honestly says data flows through the connection service read-only and is deletable (sync/index.ts:77-85) — a relay, not local-only.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>DELIVERED (nuanced)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>The in-app copy is honest. Make sure marketing copy matches the same honest framing, never "we never see your data."</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>DELIVERED — in-app copy is honest; keep marketing copy to the same standard (your side, when written)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Strategy · market-comparison hook</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>"How you're doing against the market" is the weekly habit hook.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Works today on an unofficial free price feed (marketData.ts:25); the keyed-provider seam is ready but the provider decision is open.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FOUNDER-GATED</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>The core hook rides an endpoint that can break without notice. The price-provider decision is the highest-leverage open external.</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>ONE-PAGER DELIVERED — awaiting your pick · docs/FCC-core-55-70/price-provider-onepager-v1-2026-07-29.xlsx (recommend Intrinio, fallback Twelve Data Venture; your 2-minute email inside)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Strategy · out-of-scope surfaces still shipped</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Estate, insurance, deep tax organizer are out of scope for v1.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>The pre-FCC screens still exist and are routed (app/estate.tsx, insurance.tsx, tax-organizer.tsx, itemize.tsx, jobsafety.tsx, credit.tsx).</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>OPEN DECISION</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Keep them (extra value, review burden) or hide them for launch (focus, less to test). 97-row sign-off includes them either way — your call.</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-07-28 — keep in v1; the five modules stay in your 97-row sign-off walk (action item 41)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Lineage · market average duplicated</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The market-comparison number comes from one shared helper.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Identical formula pasted inline in BOTH Home and Invest (HomeScreen.tsx:151-155, PerformanceScreen.tsx:72-74). Two auditors confirmed.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>CODE GAP</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Values agree today because the copies match. One edit to one copy breaks your one-number rule silently. Extract the helper + agreement pin.</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>BUILT — riding Build 46 (v1.1.0 #46, CUT 2026-07-29) · pinned by tests · walk it on TestFlight</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Lineage · Roth math orphaned</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The Roth screen computes its tax-now via the shared rothConversion helper.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>The screen does its own inline marginal-tax math; the helper has zero callers (RothScreen.tsx:46).</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>CODE GAP</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Same one-number risk. Either wire the helper or delete it — an orphaned duplicate concept is a trap.</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Lineage · two savings-capacity helpers</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>One capacity concept.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Goals uses one helper, multi-goal/cash-flow another; they coexist (GoalsScreen.tsx:37 vs MultiGoalScreen.tsx:58).</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>CODE GAP</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Consolidate to one before they drift.</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Lineage · scenario-diff hand-built</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>A shared diff helper feeds the adoption sheet.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Each screen hand-builds its diff rows; adopt/revert/history machinery IS shared (useStore.ts:783-791).</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>CODE GAP</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Consolidation candidate — becomes urgent when the adoption sheet is upgraded (see Plan tab).</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PARKED — rides the adoption-sheet rebuild (action item 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Lineage · source-chip wording ×3</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>One shared source-chip component.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Three inline variants with diverging wording (NetWorthScreen.tsx:159-161 vs AccountDetailScreen.tsx:60 vs SettingsScreen.tsx:417).</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>CODE GAP</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Same fix class as the estimate chip: one component, one wording.</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Lineage · RMD growth math</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Future-year required withdrawals use the shared projection engine.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>The schedule grows balances by its own rule instead (decumulation/index.ts:47-59).</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>CODE GAP</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Minor divergence risk between the RMD table and other projections; align when touched next.</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>BUILT — Build-47 payload (2026-07-30, founder approved all 25) · pinned · suite 1,311 green</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>(coverage)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Strategy: 15 commitments checked, 11 delivered as promised. Lineage: 98 rows checked, 78 verified — the named helper really feeds the named screen.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Verified delivered: scenarios suite, confidence engine, quantified non-advice nudges, multi-goal in v1, milestones, estimate labeling, zero advice language, no parent-sharing (correctly cut).</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>The one-concept-one-helper rule holds on 78 of 98 rows; the exceptions above are the complete list.</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>— context/coverage row · nothing to build</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/FCC-core-55-70/build-analysis-july24.xlsx
+++ b/docs/FCC-core-55-70/build-analysis-july24.xlsx
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>BUILT — after build 52</t>
+          <t>BUILT — in build 52 (corrected 2026-08-12 against git)</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>BUILT — after build 52</t>
+          <t>BUILT — in build 52 (corrected 2026-08-12 against git)</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>BUILT — after build 52</t>
+          <t>BUILT — in build 52 (corrected 2026-08-12 against git)</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>BUILT — after build 52</t>
+          <t>BUILT — in build 52 (corrected 2026-08-12 against git)</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>BUILT — after build 52</t>
+          <t>BUILT — in build 52 (corrected 2026-08-12 against git)</t>
         </is>
       </c>
     </row>
